--- a/public/exports-60-250-with-coowners/29188416.xlsx
+++ b/public/exports-60-250-with-coowners/29188416.xlsx
@@ -2464,12 +2464,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131904</t>
+          <t xml:space="preserve">311131902</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
